--- a/ASML/ASML_model.xlsx
+++ b/ASML/ASML_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Folders\Job Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB30E062-6431-45B2-ABCE-60B3820F9C75}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54C31D2-009E-4BE5-A4C1-B3F7883B5211}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="2" xr2:uid="{51707531-EB79-4AAB-BA4D-315592DF6CD5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="1" xr2:uid="{51707531-EB79-4AAB-BA4D-315592DF6CD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="5" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="321">
   <si>
     <t>Revenue Schedule</t>
   </si>
@@ -1057,6 +1057,9 @@
       </rPr>
       <t xml:space="preserve"> Millions)</t>
     </r>
+  </si>
+  <si>
+    <t>Yasen Georgiev</t>
   </si>
 </sst>
 </file>
@@ -1992,7 +1995,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="543">
+  <cellXfs count="544">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2865,9 +2868,6 @@
     <xf numFmtId="176" fontId="12" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="176" fontId="12" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="170" fontId="25" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
@@ -2876,6 +2876,10 @@
     <xf numFmtId="10" fontId="12" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="170" fontId="25" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -7571,7 +7575,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{8856695E-B0B2-478B-8402-E95F91B72244}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{8F755CF7-5129-4258-9315-96DC3E2EB3D1}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7582,12 +7586,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L13:P13</xm:f>
-              <xm:sqref>F13</xm:sqref>
+              <xm:f>Summary!L123:P123</xm:f>
+              <xm:sqref>F123</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{50282D9B-3BB5-47E2-A008-862F44DB1067}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{6E299932-4CD3-4FC6-985F-397DA9E5A7D4}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7598,12 +7602,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L17:P17</xm:f>
-              <xm:sqref>F17</xm:sqref>
+              <xm:f>Summary!L121:P121</xm:f>
+              <xm:sqref>F121</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{E84DEBB7-6CB3-40FD-9BC5-38DCED78E4F6}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{7AC1872C-03CB-4A94-8847-1E1D095E3E7E}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7614,12 +7618,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L22:P22</xm:f>
-              <xm:sqref>F22</xm:sqref>
+              <xm:f>Summary!L117:P117</xm:f>
+              <xm:sqref>F117</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{4AE9959F-1EEE-4D05-9623-5E22B46556D7}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{FB8FF861-B6F4-41D9-B3B2-466789F484DC}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7630,12 +7634,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L28:P28</xm:f>
-              <xm:sqref>F28</xm:sqref>
+              <xm:f>Summary!L114:P114</xm:f>
+              <xm:sqref>F114</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{5B62A18A-B73E-4811-AB0C-779BF35EC3FB}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{A8C71020-D0D1-4BDC-94A4-B7C058E8E6FD}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7646,8 +7650,152 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L31:P31</xm:f>
-              <xm:sqref>F31</xm:sqref>
+              <xm:f>Summary!L108:P108</xm:f>
+              <xm:sqref>F108</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3B0C40D1-FA8C-4732-8600-A45A06A7EB94}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L103:P103</xm:f>
+              <xm:sqref>F103</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{90ACB63A-B8D9-4ACF-AEF4-515D8432DE27}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L99:P99</xm:f>
+              <xm:sqref>F99</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{DF8D4FB8-6042-4437-8E89-9188A05C5988}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L80:P80</xm:f>
+              <xm:sqref>F80</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{B70BA9B5-A635-4DA6-B988-8CFF1B0063E1}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L78:P78</xm:f>
+              <xm:sqref>F78</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3DCF8D31-16C4-4694-AE44-4DA01DD85BEF}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L74:P74</xm:f>
+              <xm:sqref>F74</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{832BB867-837A-478E-9DFA-A8E369CCD7A4}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L71:P71</xm:f>
+              <xm:sqref>F71</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{7852AB12-2407-430B-A991-24455905E44F}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L65:P65</xm:f>
+              <xm:sqref>F65</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{50602A3D-6293-487C-A23B-757E02873D54}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L60:P60</xm:f>
+              <xm:sqref>F60</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{9033308F-8A38-4A8B-A2D4-EDF4B607282E}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Summary!L56:P56</xm:f>
+              <xm:sqref>F56</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -7671,7 +7819,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{9033308F-8A38-4A8B-A2D4-EDF4B607282E}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{5B62A18A-B73E-4811-AB0C-779BF35EC3FB}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7682,12 +7830,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L56:P56</xm:f>
-              <xm:sqref>F56</xm:sqref>
+              <xm:f>Summary!L31:P31</xm:f>
+              <xm:sqref>F31</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{50602A3D-6293-487C-A23B-757E02873D54}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{4AE9959F-1EEE-4D05-9623-5E22B46556D7}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7698,12 +7846,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L60:P60</xm:f>
-              <xm:sqref>F60</xm:sqref>
+              <xm:f>Summary!L28:P28</xm:f>
+              <xm:sqref>F28</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{7852AB12-2407-430B-A991-24455905E44F}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{E84DEBB7-6CB3-40FD-9BC5-38DCED78E4F6}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7714,12 +7862,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L65:P65</xm:f>
-              <xm:sqref>F65</xm:sqref>
+              <xm:f>Summary!L22:P22</xm:f>
+              <xm:sqref>F22</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{832BB867-837A-478E-9DFA-A8E369CCD7A4}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{50282D9B-3BB5-47E2-A008-862F44DB1067}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7730,12 +7878,12 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L71:P71</xm:f>
-              <xm:sqref>F71</xm:sqref>
+              <xm:f>Summary!L17:P17</xm:f>
+              <xm:sqref>F17</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3DCF8D31-16C4-4694-AE44-4DA01DD85BEF}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{8856695E-B0B2-478B-8402-E95F91B72244}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -7746,152 +7894,8 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>Summary!L74:P74</xm:f>
-              <xm:sqref>F74</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{B70BA9B5-A635-4DA6-B988-8CFF1B0063E1}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L78:P78</xm:f>
-              <xm:sqref>F78</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{DF8D4FB8-6042-4437-8E89-9188A05C5988}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L80:P80</xm:f>
-              <xm:sqref>F80</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{90ACB63A-B8D9-4ACF-AEF4-515D8432DE27}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L99:P99</xm:f>
-              <xm:sqref>F99</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3B0C40D1-FA8C-4732-8600-A45A06A7EB94}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L103:P103</xm:f>
-              <xm:sqref>F103</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{A8C71020-D0D1-4BDC-94A4-B7C058E8E6FD}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L108:P108</xm:f>
-              <xm:sqref>F108</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{FB8FF861-B6F4-41D9-B3B2-466789F484DC}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L114:P114</xm:f>
-              <xm:sqref>F114</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{7AC1872C-03CB-4A94-8847-1E1D095E3E7E}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L117:P117</xm:f>
-              <xm:sqref>F117</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{6E299932-4CD3-4FC6-985F-397DA9E5A7D4}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L121:P121</xm:f>
-              <xm:sqref>F121</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{8F755CF7-5129-4258-9315-96DC3E2EB3D1}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Summary!L123:P123</xm:f>
-              <xm:sqref>F123</xm:sqref>
+              <xm:f>Summary!L13:P13</xm:f>
+              <xm:sqref>F13</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -7903,7 +7907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E53C80-0B67-4457-9A05-400EEEBA9A93}">
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:Y1005"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="137"/>
@@ -9049,6 +9053,11 @@
       </c>
       <c r="Q74" s="378">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="1005" spans="25:25" x14ac:dyDescent="0.25">
+      <c r="Y1005" s="543" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -10185,19 +10194,19 @@
       <c r="D68" s="192"/>
       <c r="E68" s="192"/>
       <c r="F68" s="167"/>
-      <c r="G68" s="535">
+      <c r="G68" s="534">
         <v>0.12</v>
       </c>
-      <c r="H68" s="536">
+      <c r="H68" s="535">
         <v>0.11</v>
       </c>
-      <c r="I68" s="536">
+      <c r="I68" s="535">
         <v>0.1</v>
       </c>
-      <c r="J68" s="536">
+      <c r="J68" s="535">
         <v>0.09</v>
       </c>
-      <c r="K68" s="537">
+      <c r="K68" s="536">
         <v>0.08</v>
       </c>
     </row>
@@ -10210,7 +10219,7 @@
       <c r="D69" s="192"/>
       <c r="E69" s="192"/>
       <c r="F69" s="167"/>
-      <c r="G69" s="538">
+      <c r="G69" s="537">
         <v>0.15</v>
       </c>
       <c r="H69" s="254">
@@ -10222,7 +10231,7 @@
       <c r="J69" s="254">
         <v>0.12</v>
       </c>
-      <c r="K69" s="539">
+      <c r="K69" s="538">
         <v>0.11</v>
       </c>
     </row>
@@ -10235,19 +10244,19 @@
       <c r="D70" s="192"/>
       <c r="E70" s="192"/>
       <c r="F70" s="167"/>
-      <c r="G70" s="540">
+      <c r="G70" s="539">
         <v>0.08</v>
       </c>
-      <c r="H70" s="541">
+      <c r="H70" s="540">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I70" s="541">
+      <c r="I70" s="540">
         <v>0.06</v>
       </c>
-      <c r="J70" s="541">
+      <c r="J70" s="540">
         <v>0.06</v>
       </c>
-      <c r="K70" s="542">
+      <c r="K70" s="541">
         <v>0.05</v>
       </c>
     </row>
@@ -10349,19 +10358,19 @@
       <c r="D77" s="195"/>
       <c r="E77" s="195"/>
       <c r="F77" s="167"/>
-      <c r="G77" s="535">
+      <c r="G77" s="534">
         <v>0.52</v>
       </c>
-      <c r="H77" s="536">
+      <c r="H77" s="535">
         <v>0.53</v>
       </c>
-      <c r="I77" s="536">
+      <c r="I77" s="535">
         <v>0.54</v>
       </c>
-      <c r="J77" s="536">
+      <c r="J77" s="535">
         <v>0.55000000000000004</v>
       </c>
-      <c r="K77" s="537">
+      <c r="K77" s="536">
         <v>0.56000000000000005</v>
       </c>
     </row>
@@ -10374,7 +10383,7 @@
       <c r="D78" s="195"/>
       <c r="E78" s="195"/>
       <c r="F78" s="167"/>
-      <c r="G78" s="538">
+      <c r="G78" s="537">
         <v>0.54</v>
       </c>
       <c r="H78" s="254">
@@ -10386,7 +10395,7 @@
       <c r="J78" s="254">
         <v>0.59</v>
       </c>
-      <c r="K78" s="539">
+      <c r="K78" s="538">
         <v>0.6</v>
       </c>
     </row>
@@ -10399,19 +10408,19 @@
       <c r="D79" s="195"/>
       <c r="E79" s="195"/>
       <c r="F79" s="167"/>
-      <c r="G79" s="540">
+      <c r="G79" s="539">
         <v>0.5</v>
       </c>
-      <c r="H79" s="541">
+      <c r="H79" s="540">
         <v>0.5</v>
       </c>
-      <c r="I79" s="541">
+      <c r="I79" s="540">
         <v>0.51</v>
       </c>
-      <c r="J79" s="541">
+      <c r="J79" s="540">
         <v>0.51</v>
       </c>
-      <c r="K79" s="542">
+      <c r="K79" s="541">
         <v>0.52</v>
       </c>
     </row>
@@ -22512,14 +22521,14 @@
       <c r="I66" s="155"/>
       <c r="J66" s="155"/>
       <c r="K66" s="330"/>
-      <c r="L66" s="534">
+      <c r="L66" s="542">
         <f>SUM(L65:P65)</f>
         <v>36649.066136841167</v>
       </c>
-      <c r="M66" s="534"/>
-      <c r="N66" s="534"/>
-      <c r="O66" s="534"/>
-      <c r="P66" s="534"/>
+      <c r="M66" s="542"/>
+      <c r="N66" s="542"/>
+      <c r="O66" s="542"/>
+      <c r="P66" s="542"/>
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="19"/>
